--- a/data/incoming/inventory/BRU-0001_inventory_2026-10-05.xlsx
+++ b/data/incoming/inventory/BRU-0001_inventory_2026-10-05.xlsx
@@ -358,7 +358,7 @@
         <v>7</v>
       </c>
       <c r="C4" s="1">
-        <v>554.0</v>
+        <v>54.0</v>
       </c>
       <c r="D4" s="2">
         <v>46300.333333333336</v>
